--- a/uploads/today.xlsx
+++ b/uploads/today.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F794991A-FCDD-46BF-880A-D28F4648796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2668B3D6-563E-42ED-8B50-FF7BD74B1E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D32D089-C1C8-423A-82F7-25D73034A165}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>first_name</t>
   </si>
@@ -53,13 +53,19 @@
     <t>Malama</t>
   </si>
   <si>
-    <t>Jane</t>
-  </si>
-  <si>
     <t>Chita</t>
   </si>
   <si>
-    <t>regan@mail.com</t>
+    <t>Janes</t>
+  </si>
+  <si>
+    <t>Malamaa</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>one@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -465,32 +471,36 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D2">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{D03C71CE-87E4-4FB9-94E5-0193BBECB670}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{5F5BEF41-DE64-4C90-AB7A-E82F1D8A0D0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
